--- a/data/trans_camb/POLIPATOLOGIA_5-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_5-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 5,06</t>
+          <t>0,06; 5,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 4,36</t>
+          <t>-0,37; 4,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,37; 18,51</t>
+          <t>11,64; 18,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 9,68</t>
+          <t>3,87; 9,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,81; 11,61</t>
+          <t>4,85; 11,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,67; 28,4</t>
+          <t>21,34; 28,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,03; 7,04</t>
+          <t>3,33; 7,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,68</t>
+          <t>3,29; 7,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,4; 23,39</t>
+          <t>18,61; 23,61</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 78,59</t>
+          <t>-0,43; 83,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 69,61</t>
+          <t>-5,23; 78,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>134,15; 293,85</t>
+          <t>138,77; 301,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,19; 79,2</t>
+          <t>24,93; 79,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,96; 95,25</t>
+          <t>33,69; 98,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>148,63; 238,32</t>
+          <t>143,3; 239,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,64; 72,03</t>
+          <t>29,08; 73,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,35; 78,23</t>
+          <t>29,03; 77,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>159,75; 240,41</t>
+          <t>163,96; 248,51</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,74</t>
+          <t>-0,91; 0,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,21</t>
+          <t>-0,53; 1,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,68</t>
+          <t>2,48; 5,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 2,41</t>
+          <t>-0,32; 2,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,57</t>
+          <t>1,54; 4,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,46; 38,77</t>
+          <t>7,46; 36,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 1,15</t>
+          <t>-0,34; 1,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,5</t>
+          <t>0,88; 2,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,61; 25,01</t>
+          <t>5,62; 24,27</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-45,57; 70,55</t>
+          <t>-45,9; 67,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,36; 112,44</t>
+          <t>-27,66; 114,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>141,69; 537,02</t>
+          <t>136,69; 531,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 106,1</t>
+          <t>-9,49; 97,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,08; 204,65</t>
+          <t>40,12; 193,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>240,71; 1668,82</t>
+          <t>244,81; 1686,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 64,49</t>
+          <t>-13,14; 65,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,33; 140,57</t>
+          <t>34,17; 135,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>239,35; 1246,43</t>
+          <t>236,31; 1182,27</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,08</t>
+          <t>-2,49; 1,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,9</t>
+          <t>-1,97; 1,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 3,66</t>
+          <t>-0,03; 3,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 3,8</t>
+          <t>-0,43; 3,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 3,53</t>
+          <t>-0,56; 3,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,44; 8,86</t>
+          <t>4,6; 8,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,97</t>
+          <t>-0,97; 1,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 2,02</t>
+          <t>-0,64; 2,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,81; 5,59</t>
+          <t>2,98; 5,79</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-89,18; 133,35</t>
+          <t>-87,89; 116,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-64,73; 160,01</t>
+          <t>-66,28; 149,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 277,49</t>
+          <t>-4,59; 290,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 411,61</t>
+          <t>-24,0; 452,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,39; 357,69</t>
+          <t>-26,1; 425,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>146,88; 924,25</t>
+          <t>137,51; 885,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-43,26; 156,0</t>
+          <t>-38,42; 146,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,44; 150,1</t>
+          <t>-29,86; 158,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>96,88; 440,54</t>
+          <t>103,53; 443,58</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,31</t>
+          <t>-0,49; 1,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,02</t>
+          <t>-0,71; 1,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,8</t>
+          <t>2,71; 5,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,51</t>
+          <t>1,86; 4,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,42</t>
+          <t>1,72; 4,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,1; 29,19</t>
+          <t>9,2; 29,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,63</t>
+          <t>0,92; 2,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,51</t>
+          <t>0,79; 2,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,6; 18,52</t>
+          <t>6,52; 18,19</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 42,44</t>
+          <t>-13,68; 42,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,78; 33,97</t>
+          <t>-18,83; 38,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77,48; 187,45</t>
+          <t>79,22; 198,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25,06; 72,55</t>
+          <t>25,05; 73,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,65; 73,23</t>
+          <t>23,36; 72,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>132,0; 444,26</t>
+          <t>134,53; 474,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,49; 56,33</t>
+          <t>17,01; 55,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,39; 52,7</t>
+          <t>14,63; 52,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>126,44; 369,11</t>
+          <t>125,01; 372,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/POLIPATOLOGIA_5-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_5-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14,89</t>
+          <t>13,68</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,85</t>
+          <t>24,16</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21,02</t>
+          <t>19,99</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 5,18</t>
+          <t>0,2; 5,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 4,71</t>
+          <t>-0,06; 4,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,64; 18,4</t>
+          <t>10,7; 17,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,87; 9,65</t>
+          <t>3,95; 9,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,85; 11,41</t>
+          <t>5,02; 11,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,34; 28,01</t>
+          <t>21,02; 27,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 7,17</t>
+          <t>3,2; 7,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,29; 7,59</t>
+          <t>3,3; 7,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,61; 23,61</t>
+          <t>17,51; 22,47</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>206,06%</t>
+          <t>189,38%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>189,28%</t>
+          <t>183,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>199,51%</t>
+          <t>189,75%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 83,79</t>
+          <t>2,22; 83,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 78,38</t>
+          <t>-0,78; 78,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>138,77; 301,31</t>
+          <t>129,12; 291,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,93; 79,72</t>
+          <t>26,73; 84,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,69; 98,31</t>
+          <t>35,58; 97,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>143,3; 239,02</t>
+          <t>142,68; 229,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,08; 73,9</t>
+          <t>27,37; 74,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,03; 77,79</t>
+          <t>29,49; 77,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>163,96; 248,51</t>
+          <t>152,65; 234,31</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,35</t>
+          <t>5,01</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,11</t>
+          <t>8,28</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10,18</t>
+          <t>6,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,72</t>
+          <t>-0,92; 0,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,23</t>
+          <t>-0,49; 1,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,68</t>
+          <t>3,95; 6,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,24</t>
+          <t>-0,28; 2,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,44</t>
+          <t>1,65; 4,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,46; 36,29</t>
+          <t>6,85; 9,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,15</t>
+          <t>-0,32; 1,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,44</t>
+          <t>0,86; 2,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 24,27</t>
+          <t>5,79; 7,57</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>288,17%</t>
+          <t>331,81%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>562,6%</t>
+          <t>288,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>470,12%</t>
+          <t>306,35%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-45,9; 67,31</t>
+          <t>-46,02; 65,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,66; 114,63</t>
+          <t>-26,14; 116,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>136,69; 531,16</t>
+          <t>184,97; 579,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 97,57</t>
+          <t>-10,84; 104,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,12; 193,49</t>
+          <t>44,4; 194,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>244,81; 1686,2</t>
+          <t>181,51; 428,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 65,7</t>
+          <t>-12,75; 68,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,17; 135,48</t>
+          <t>32,26; 135,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>236,31; 1182,27</t>
+          <t>222,15; 441,78</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>1,95</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,61</t>
+          <t>6,76</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,26</t>
+          <t>4,38</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,23</t>
+          <t>-2,63; 1,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,68</t>
+          <t>-2,12; 1,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 3,71</t>
+          <t>-0,03; 3,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 3,97</t>
+          <t>-0,36; 4,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 3,61</t>
+          <t>-0,66; 3,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 8,74</t>
+          <t>4,65; 8,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,96</t>
+          <t>-1,04; 1,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,09</t>
+          <t>-0,72; 2,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,98; 5,79</t>
+          <t>2,95; 5,75</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>374,77%</t>
+          <t>383,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>217,4%</t>
+          <t>223,37%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-87,89; 116,86</t>
+          <t>-88,21; 127,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-66,28; 149,45</t>
+          <t>-68,59; 180,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 290,18</t>
+          <t>-7,33; 305,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,0; 452,64</t>
+          <t>-23,32; 407,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-26,1; 425,34</t>
+          <t>-39,05; 330,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>137,51; 885,64</t>
+          <t>156,38; 976,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-38,42; 146,27</t>
+          <t>-44,42; 119,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,86; 158,66</t>
+          <t>-29,49; 144,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>103,53; 443,58</t>
+          <t>107,02; 444,99</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,53</t>
+          <t>4,98</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,29</t>
+          <t>9,69</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9,57</t>
+          <t>7,42</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,3</t>
+          <t>-0,46; 1,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,11</t>
+          <t>-0,73; 0,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,66</t>
+          <t>3,93; 6,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,49</t>
+          <t>1,89; 4,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,44</t>
+          <t>1,85; 4,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,2; 29,24</t>
+          <t>8,38; 10,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,63</t>
+          <t>1,0; 2,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,44</t>
+          <t>0,84; 2,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,52; 18,19</t>
+          <t>6,56; 8,29</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>132,59%</t>
+          <t>145,78%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>213,1%</t>
+          <t>144,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>188,16%</t>
+          <t>145,94%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 42,3</t>
+          <t>-12,61; 43,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 38,56</t>
+          <t>-19,18; 32,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>79,22; 198,08</t>
+          <t>101,12; 204,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25,05; 73,11</t>
+          <t>24,89; 71,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,36; 72,05</t>
+          <t>24,8; 73,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>134,53; 474,32</t>
+          <t>112,65; 184,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,01; 55,37</t>
+          <t>18,88; 55,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,63; 52,35</t>
+          <t>15,4; 53,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>125,01; 372,88</t>
+          <t>119,17; 180,18</t>
         </is>
       </c>
     </row>
